--- a/planning/Book1.xlsx
+++ b/planning/Book1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\gambler-bevy\planning\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\Obsidian Vault\GamblerEditorBevy\planning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3DDE752-B86B-45E2-8E9B-BA77892554BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3755AEDB-A7FC-4AC2-91E4-4152C74C4B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" activeTab="1" xr2:uid="{0AFE7B45-6DF7-449F-A4E2-BEA922B056F4}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="181">
   <si>
     <t>A</t>
   </si>
@@ -168,18 +168,12 @@
     <t>Helios</t>
   </si>
   <si>
-    <t>Libertas</t>
-  </si>
-  <si>
     <t>Apollo</t>
   </si>
   <si>
     <t>Samson</t>
   </si>
   <si>
-    <t>Lamieroux</t>
-  </si>
-  <si>
     <t>Babel</t>
   </si>
   <si>
@@ -201,9 +195,6 @@
     <t>The Hermit</t>
   </si>
   <si>
-    <t>Chekhov</t>
-  </si>
-  <si>
     <t>Geb</t>
   </si>
   <si>
@@ -213,33 +204,12 @@
     <t>Croation word for justice</t>
   </si>
   <si>
-    <t>Roman Liberty godess</t>
-  </si>
-  <si>
-    <t>Selene</t>
-  </si>
-  <si>
     <t>Astraeus</t>
   </si>
   <si>
-    <t>Greek moon godess</t>
-  </si>
-  <si>
-    <t>Greek sun god</t>
-  </si>
-  <si>
-    <t>Greek star titan</t>
-  </si>
-  <si>
     <t>Abrahamic</t>
   </si>
   <si>
-    <t>Author</t>
-  </si>
-  <si>
-    <t>French name lol</t>
-  </si>
-  <si>
     <t>yeah</t>
   </si>
   <si>
@@ -435,9 +405,6 @@
     <t>Kale's dnd name</t>
   </si>
   <si>
-    <t>Checkhov's gun, idk gambling is the name of the game we gonna have a gamble boss bitch (idk)</t>
-  </si>
-  <si>
     <t>symbolic of power, potential, and the unification of the physical and spiritual worlds.</t>
   </si>
   <si>
@@ -556,13 +523,70 @@
   </si>
   <si>
     <t>IRL Inspo</t>
+  </si>
+  <si>
+    <t>Pat</t>
+  </si>
+  <si>
+    <t>"lucky" or at least appears lucky</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> bi-polar tendencies, never know what youll run into</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not really lucky, very unfortunate actually but would not appear so, maybe a belief that they are not lucky when they really are? </t>
+  </si>
+  <si>
+    <t>Could be cool to input-rng this boss to have different phaze orders</t>
+  </si>
+  <si>
+    <t>Lupous</t>
+  </si>
+  <si>
+    <t>ropes, entire arena flips over? Cool fight ideas</t>
+  </si>
+  <si>
+    <t>Imperius from diablo vibes? Need to make it different</t>
+  </si>
+  <si>
+    <t>Too self-critical, does not feel "worthy to judge" but is in that role</t>
+  </si>
+  <si>
+    <t>Cody</t>
+  </si>
+  <si>
+    <t>é</t>
+  </si>
+  <si>
+    <t>Lucé</t>
+  </si>
+  <si>
+    <t>Danny</t>
+  </si>
+  <si>
+    <t>Travis</t>
+  </si>
+  <si>
+    <t>Artistic compliments to cody</t>
+  </si>
+  <si>
+    <t>Saturn</t>
+  </si>
+  <si>
+    <t>Green Sun Titan</t>
+  </si>
+  <si>
+    <t>Green Moon Titan (not really)</t>
+  </si>
+  <si>
+    <t>Greek Star Titan</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -584,6 +608,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -761,7 +791,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -793,7 +823,16 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1149,33 +1188,33 @@
   <sheetData>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F3" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="G3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F4" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="G4" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1223,23 +1262,23 @@
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="G7" s="20"/>
       <c r="H7" s="20" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="I7" s="20"/>
       <c r="J7" s="20"/>
@@ -1252,19 +1291,19 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G8" s="21"/>
       <c r="H8" s="21"/>
@@ -1274,31 +1313,31 @@
       <c r="L8" s="21"/>
       <c r="M8" s="21"/>
       <c r="N8" s="21" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="O8" s="21"/>
       <c r="P8" s="21"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="17"/>
       <c r="I9" s="17" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
@@ -1310,68 +1349,68 @@
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="N12" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
@@ -1388,10 +1427,10 @@
     </row>
     <row r="14" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="19"/>
@@ -1404,14 +1443,14 @@
       <c r="L14" s="19"/>
       <c r="M14" s="19"/>
       <c r="N14" s="19" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="O14" s="19"/>
       <c r="P14" s="19"/>
     </row>
     <row r="24" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H24" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
@@ -1456,10 +1495,10 @@
         <v>32</v>
       </c>
       <c r="D39" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E39" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
@@ -1470,10 +1509,10 @@
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E40" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
@@ -1501,51 +1540,51 @@
     <col min="8" max="8" width="43" customWidth="1"/>
     <col min="9" max="9" width="45.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="35.140625" customWidth="1"/>
-    <col min="11" max="11" width="25.7109375" customWidth="1"/>
+    <col min="11" max="11" width="25.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B1" s="24"/>
-      <c r="C1" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="C1" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
       <c r="I1" s="24"/>
       <c r="J1" s="24"/>
       <c r="K1" s="24"/>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="24"/>
-      <c r="C2" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="E2" s="25" t="s">
+      <c r="C2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="F2" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="G2" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="3" spans="2:11" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1556,25 +1595,25 @@
         <v>4</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="F3" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="K3" s="23" t="s">
         <v>129</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="I3" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="J3" s="23" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
@@ -1585,22 +1624,23 @@
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F4" s="23"/>
       <c r="G4" s="23"/>
       <c r="H4" s="23" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="J4" s="23" t="s">
-        <v>142</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="K4" s="23"/>
     </row>
     <row r="5" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
@@ -1610,22 +1650,23 @@
         <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F5" s="23"/>
       <c r="G5" s="23"/>
       <c r="H5" s="23" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="J5" s="23" t="s">
-        <v>144</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="K5" s="23"/>
     </row>
     <row r="6" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
@@ -1635,22 +1676,23 @@
         <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F6" s="23"/>
       <c r="G6" s="23"/>
       <c r="H6" s="23" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="J6" s="23" t="s">
-        <v>138</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="K6" s="23"/>
     </row>
     <row r="7" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
@@ -1660,22 +1702,23 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="23"/>
       <c r="H7" s="23" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>148</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="K7" s="23"/>
     </row>
     <row r="8" spans="2:11" ht="60" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
@@ -1685,26 +1728,26 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="23" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="K8" t="s">
-        <v>158</v>
+        <v>149</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="60" x14ac:dyDescent="0.25">
@@ -1715,26 +1758,26 @@
         <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="23" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="K9" t="s">
-        <v>164</v>
+        <v>155</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
@@ -1745,16 +1788,17 @@
         <v>11</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="23"/>
       <c r="H10" s="23"/>
       <c r="I10" s="23"/>
       <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
@@ -1764,37 +1808,45 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F11" s="23"/>
       <c r="G11" s="23"/>
       <c r="H11" s="23"/>
       <c r="I11" s="23"/>
       <c r="J11" s="23"/>
-    </row>
-    <row r="12" spans="2:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="K11" s="23"/>
+    </row>
+    <row r="12" spans="2:11" ht="45" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>10</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>165</v>
+      </c>
       <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-    </row>
-    <row r="13" spans="2:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="J12" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="90" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <v>11</v>
       </c>
@@ -1802,44 +1854,46 @@
         <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="23"/>
       <c r="H13" s="23" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="J13" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="K13" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <v>12</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="23"/>
+      <c r="D14" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25" t="s">
+        <v>27</v>
+      </c>
       <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
+      <c r="K14" s="23" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
@@ -1852,15 +1906,16 @@
         <v>41</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
-    </row>
-    <row r="16" spans="2:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="K15" s="23"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <v>14</v>
       </c>
@@ -1868,37 +1923,43 @@
         <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F16" s="23"/>
       <c r="G16" s="23"/>
       <c r="H16" s="23"/>
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="23"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <v>15</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
+      <c r="E17" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="F17" s="28"/>
+      <c r="G17" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>176</v>
+      </c>
       <c r="I17" s="23"/>
       <c r="J17" s="23"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="23"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <v>16</v>
       </c>
@@ -1906,94 +1967,107 @@
         <v>19</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F18" s="23"/>
       <c r="G18" s="23"/>
       <c r="H18" s="23"/>
       <c r="I18" s="23"/>
       <c r="J18" s="23"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K18" s="23"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <v>17</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19" s="23"/>
+      <c r="D19" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>171</v>
+      </c>
       <c r="G19" s="23"/>
       <c r="H19" s="23"/>
       <c r="I19" s="23"/>
       <c r="J19" s="23"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K19" s="23"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
         <v>18</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="23"/>
+      <c r="D20" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>175</v>
+      </c>
       <c r="G20" s="23"/>
       <c r="H20" s="23"/>
       <c r="I20" s="23"/>
       <c r="J20" s="23"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K20" s="23"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="3">
         <v>19</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="23"/>
+      <c r="E21" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>174</v>
+      </c>
       <c r="G21" s="23"/>
       <c r="H21" s="23"/>
       <c r="I21" s="23"/>
       <c r="J21" s="23"/>
-    </row>
-    <row r="22" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="K21" s="23"/>
+    </row>
+    <row r="22" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <v>20</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="F22" s="23"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25" t="s">
+        <v>26</v>
+      </c>
       <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
+      <c r="H22" s="23" t="s">
+        <v>169</v>
+      </c>
       <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-    </row>
-    <row r="23" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="J22" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="K22" s="23"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <v>21</v>
       </c>
@@ -2001,16 +2075,17 @@
         <v>24</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F23" s="23"/>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
       <c r="I23" s="23"/>
       <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
